--- a/rsvp/wedding_guests.xlsx
+++ b/rsvp/wedding_guests.xlsx
@@ -22,22 +22,22 @@
     <t>Phone Number (with country code)</t>
   </si>
   <si>
-    <t>Jia Xin</t>
-  </si>
-  <si>
-    <t>+6596502691</t>
-  </si>
-  <si>
-    <t>Brehmer</t>
-  </si>
-  <si>
-    <t>+6590098431</t>
-  </si>
-  <si>
-    <t>Bee Yen</t>
-  </si>
-  <si>
-    <t>+6581273318</t>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>+6598765432</t>
+  </si>
+  <si>
+    <t>Bain</t>
+  </si>
+  <si>
+    <t>+6591234567</t>
+  </si>
+  <si>
+    <t>Catherine</t>
+  </si>
+  <si>
+    <t>+6591212121</t>
   </si>
 </sst>
 </file>
@@ -61,7 +61,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
